--- a/backend/data/sample/pa_dialog_eval_sample.xlsx
+++ b/backend/data/sample/pa_dialog_eval_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF14"/>
+  <dimension ref="A1:BF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,11 +778,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -792,11 +788,7 @@
           <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;抱歉,我暂时无法处理该业务。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -829,16 +821,8 @@
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>常规意图</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>小安</t>
-        </is>
-      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr">
         <is>
           <t>是</t>
@@ -846,7 +830,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr"/>
@@ -855,16 +839,8 @@
           <t>证券</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>分发错误—BU多分</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
@@ -907,7 +883,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>帮我解锁消费权益</t>
+          <t>春节红包活动规则</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -958,13 +934,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>咨询客服</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>咨询客服智能体</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
@@ -973,12 +953,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>LLMIntent活动场景</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -993,16 +973,8 @@
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>选股意图</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>小安</t>
-        </is>
-      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr">
         <is>
           <t>是</t>
@@ -1010,14 +982,10 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr">
         <is>
           <t>证券</t>
@@ -1025,10 +993,14 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>分发错误—非本BU业务</t>
+        </is>
+      </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1071,7 +1043,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>权益怎么用</t>
+          <t>我的自选股今天表现如何</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1103,7 +1075,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1117,18 +1089,22 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;点击【去使用】即可在对应模块体验权益。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"小安\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;您的自选股今日:平安银行 +1.2%,贵州茅台 -0.5%,宁德时代 +2.1%。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>自选</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>自选智能体</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1137,17 +1113,17 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>上下文延续</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>00455</t>
+          <t>015a9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1157,16 +1133,8 @@
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>选股意图</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>小安</t>
-        </is>
-      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr">
         <is>
           <t>是</t>
@@ -1177,11 +1145,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr">
         <is>
           <t>证券</t>
@@ -1235,7 +1199,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>可转债权限开通条件</t>
+          <t>帮我卖出1000股宁德时代</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1281,18 +1245,22 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;尊敬的客户,可转债开通条件:&lt;/p&gt;&lt;p&gt;✅ 20个交易日日均资产≥10万&lt;/p&gt;&lt;p&gt;✅ 参与证券交易24个月以上&lt;/p&gt;&lt;p&gt;✅ 风险测评C3/C4/C5&lt;/p&gt;&lt;p&gt;✅ 通过可转债知识测评&lt;/p&gt;&lt;p&gt;开通方式:&lt;a href=\\\"javascript:void(0)\\\" onclick=\\\"sign()\\\"&gt;点击这里签署协议&lt;/a&gt;&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"可转债开通\"}, \"stQuestion\": \"可转债权限开通条件\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;已为您下单卖出宁德时代1000股,如需人工协助点击&lt;a href=\\\"javascript:void(0)\\\" onclick=\\\"fTrans2Manual()\\\"&gt;【转人工】&lt;/a&gt;&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"卖出委托\"}, \"stQuestion\": \"如何卖出股票\", \"bot_name\": \"交易智能体\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>资产查询</t>
+          <t>交易</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>交易智能体</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1306,12 +1274,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>FAQ命中</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>015a9</t>
+          <t>021bd</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1321,16 +1289,8 @@
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>常规意图</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>自研指令</t>
-        </is>
-      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr">
         <is>
           <t>是</t>
@@ -1395,7 +1355,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>人工服务</t>
+          <t>我的总资产多少</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1441,18 +1401,22 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;点击&lt;a href=\\\"javascript:void(0)\\\" onclick=\\\"fTrans2Manual()\\\"&gt;【转人工】&lt;/a&gt;&lt;/p&gt;&lt;p&gt;电话95511-8-9-1(交易日9:00-18:00)&lt;/p&gt;&lt;p&gt;也可直播咨询。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"转人工服务\"}, \"stQuestion\": \"平安证券客服电话和服务时间\", \"bot_name\": \"自研指令\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;您的账户总资产为 52.3 万元,可用资金 8.1 万元。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>咨询客服</t>
+          <t>资产查询</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>资产查询智能体</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1466,12 +1430,12 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>转人工</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>021bd</t>
+          <t>03677</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1481,16 +1445,8 @@
       </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>常规意图</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>自研指令</t>
-        </is>
-      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr">
         <is>
           <t>是</t>
@@ -1555,7 +1511,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>我的融资利率年化是百分之多少</t>
+          <t>那我持有哪些股票</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1587,7 +1543,7 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1601,18 +1557,22 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;您当前融资利率年化为6.5%。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;您当前持仓:1.平安银行 2.贵州茅台 3.宁德时代。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>资产查询</t>
+          <t>查持仓</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>查持仓智能体</t>
+        </is>
+      </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
@@ -1626,7 +1586,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>资产查询</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1641,16 +1601,8 @@
       </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>常规意图</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>自研指令</t>
-        </is>
-      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr">
         <is>
           <t>是</t>
@@ -1715,7 +1667,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>我的融资成本高吗</t>
+          <t>比亚迪跌到200时提醒我</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1747,7 +1699,7 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1761,18 +1713,22 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;相较行业平均水平,您的融资成本处于中等区间。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;已为您设置:比亚迪 跌到 200 元时推送提醒。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>资产查询</t>
+          <t>到价提醒</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>到价提醒智能体</t>
+        </is>
+      </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
@@ -1786,12 +1742,12 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>上下文延续</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>03677</t>
+          <t>04a12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1801,16 +1757,8 @@
       </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>常规意图</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>自研指令</t>
-        </is>
-      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr">
         <is>
           <t>是</t>
@@ -1875,7 +1823,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>电脑上平安证券APP的持仓中怎么看不到当日盈亏</t>
+          <t>五粮液近5日主力资金流向</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1921,18 +1869,22 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;当日盈亏可在持仓页右上角切换显示,若仍看不到请检查版本。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;主力资金近5日呈净流出态势。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"股票主力资金流向分析智能体\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>查持仓</t>
+          <t>股票主力资金流向分析</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>股票主力资金流向分析智能体</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
@@ -1946,12 +1898,12 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>持仓相关</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>04a12</t>
+          <t>05c33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1961,16 +1913,8 @@
       </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>常规意图</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>自研指令</t>
-        </is>
-      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr">
         <is>
           <t>是</t>
@@ -1989,10 +1933,14 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>答案不够具体</t>
+        </is>
+      </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -2035,7 +1983,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6月12日涨停板股票封成比6月15号换手怎么算</t>
+          <t>具体每天流入流出多少</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -2067,7 +2015,7 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2081,18 +2029,22 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;封成比=封单量/成交量,换手率=成交量/流通股本。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"同花顺\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;近5日主力净额:-1.2亿、-0.8亿、+0.3亿、-2.1亿、-0.5亿。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"股票主力资金流向分析智能体\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>问诊股</t>
+          <t>股票主力资金流向分析</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>股票主力资金流向分析智能体</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
@@ -2106,7 +2058,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>行情诊断</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2121,16 +2073,8 @@
       </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>选股意图</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>同花顺</t>
-        </is>
-      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr">
         <is>
           <t>是</t>
@@ -2149,14 +2093,10 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>答案不够具体</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
@@ -2199,7 +2139,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>还是没看懂,能给个例子吗</t>
+          <t>我在哪个营业部开户的</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -2231,7 +2171,7 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2245,18 +2185,22 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;例如某股封单100万股、成交200万股,封成比即0.5。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"同花顺\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;您的开户营业部为:平安证券深圳分公司。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>问诊股</t>
+          <t>查开户营业部</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>查开户营业部智能体</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
@@ -2270,12 +2214,12 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>上下文延续</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>05c33</t>
+          <t>06d44</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2285,16 +2229,8 @@
       </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>选股意图</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>同花顺</t>
-        </is>
-      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr">
         <is>
           <t>是</t>
@@ -2359,7 +2295,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>变更开户营业部</t>
+          <t>天齐锂业最新半年报公告</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2405,18 +2341,22 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;可在APP-我的-账户管理-变更营业部办理,需身份验证。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;天齐锂业2026半年报要点:营收同比+18%。完整公告:&lt;a href=\\\"javascript:void(0)\\\" onclick=\\\"open()\\\"&gt;点击查看&lt;/a&gt;&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"查公告\"}, \"stQuestion\": \"天齐锂业半年报\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>查开户营业部</t>
+          <t>问诊股</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>问诊股智能体</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
@@ -2430,12 +2370,12 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>营业部</t>
+          <t>LLMIntent</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>06d44</t>
+          <t>07e55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2445,16 +2385,8 @@
       </c>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>常规意图</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>自研指令</t>
-        </is>
-      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr">
         <is>
           <t>是</t>
@@ -2519,7 +2451,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>银行卡变更及常见注意事项</t>
+          <t>连续3天主力净流入的股票</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -2565,18 +2497,22 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;请联系您的开户银行办理银行卡变更。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"\", \"source\": \"zongkong\"}"}]</t>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;符合条件的股票:贵州茅台、五粮液、长江电力。&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"\"}, \"stQuestion\": \"\", \"bot_name\": \"主力资金流向选股智能体\", \"source\": \"zongkong\"}"}]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>资产查询</t>
+          <t>主力资金流向选股</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>主力资金流向选股智能体</t>
+        </is>
+      </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr">
         <is>
@@ -2595,7 +2531,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>07e55</t>
+          <t>09a01</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2605,16 +2541,8 @@
       </c>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>常规意图</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>小安</t>
-        </is>
-      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr">
         <is>
           <t>是</t>
@@ -2622,7 +2550,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr"/>
@@ -2633,14 +2561,10 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>分发错误—非本BU业务</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -2683,7 +2607,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>。。。</t>
+          <t>身份证如何更新</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2727,12 +2651,24 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[{"roomMark": "person", "msgType": "aat_text", "msgContext": "{\"msgInfo\": {\"data\": {\"content\": \"&lt;p&gt;可在APP-我的-证件更新办理,或拨打客服&lt;a href=\\\"javascript:void(0)\\\" onclick=\\\"fTrans2Manual()\\\"&gt;95511-8&lt;/a&gt;&lt;/p&gt;\"}}, \"ths_intent_info\": {\"intent_name\": \"证件更新\"}, \"stQuestion\": \"身份证更新\", \"bot_name\": \"咨询客服智能体\", \"source\": \"zongkong\"}"}]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>咨询客服</t>
+        </is>
+      </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>咨询客服智能体</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr">
         <is>
@@ -2744,15 +2680,19 @@
           <t>常规</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>LLMIntent</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>08f66</t>
+          <t>0ab12</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr"/>
@@ -2764,14 +2704,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="AV14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr">
         <is>
           <t>证券</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
@@ -2780,6 +2728,138 @@
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:41:26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>正式</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>。。。</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>原生</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>LLMIntent</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>08f66</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
